--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.63475183075061</v>
+        <v>7.090647172496975</v>
       </c>
       <c r="D2" t="n">
-        <v>16.59740594612757</v>
+        <v>2.697078466245731</v>
       </c>
       <c r="E2" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F2" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.08893120291698</v>
+        <v>13.01445132047401</v>
       </c>
       <c r="D3" t="n">
-        <v>42.82458808126161</v>
+        <v>6.958995563205011</v>
       </c>
       <c r="E3" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F3" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.29780937715088</v>
+        <v>9.473394023787018</v>
       </c>
       <c r="D4" t="n">
-        <v>19.56182471403436</v>
+        <v>3.178796516030583</v>
       </c>
       <c r="E4" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F4" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.53035273261003</v>
+        <v>6.098682319049129</v>
       </c>
       <c r="D5" t="n">
-        <v>6.024830850454802</v>
+        <v>0.9790350131989054</v>
       </c>
       <c r="E5" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F5" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>48.3654788295512</v>
+        <v>7.859390309802071</v>
       </c>
       <c r="D6" t="n">
-        <v>48.45598201696725</v>
+        <v>7.874097077757178</v>
       </c>
       <c r="E6" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F6" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.76523377966079</v>
+        <v>7.274350489194878</v>
       </c>
       <c r="D7" t="n">
-        <v>28.87920169977568</v>
+        <v>4.692870276213549</v>
       </c>
       <c r="E7" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F7" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.09772110167168</v>
+        <v>1.803379679021647</v>
       </c>
       <c r="D8" t="n">
-        <v>11.94088395555507</v>
+        <v>1.940393642777698</v>
       </c>
       <c r="E8" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F8" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>56.72199753264366</v>
+        <v>9.217324599054596</v>
       </c>
       <c r="D9" t="n">
-        <v>42.9563732174866</v>
+        <v>6.980410647841572</v>
       </c>
       <c r="E9" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F9" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.98934309679749</v>
+        <v>1.948268253229593</v>
       </c>
       <c r="D10" t="n">
-        <v>11.59511884892532</v>
+        <v>1.884206812950365</v>
       </c>
       <c r="E10" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F10" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>10.93487939777035</v>
+        <v>1.776917902137682</v>
       </c>
       <c r="D11" t="n">
-        <v>10.08229583066195</v>
+        <v>1.638373072482568</v>
       </c>
       <c r="E11" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F11" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.12394813445611</v>
+        <v>6.845141571849117</v>
       </c>
       <c r="D12" t="n">
-        <v>42.02118085379735</v>
+        <v>6.82844188874207</v>
       </c>
       <c r="E12" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F12" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>17.01845393042681</v>
+        <v>2.765498763694357</v>
       </c>
       <c r="D13" t="n">
-        <v>16.09271634212326</v>
+        <v>2.61506640559503</v>
       </c>
       <c r="E13" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F13" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>30.26216915688425</v>
+        <v>4.917602487993691</v>
       </c>
       <c r="D14" t="n">
-        <v>29.53017639559796</v>
+        <v>4.798653664284669</v>
       </c>
       <c r="E14" t="n">
-        <v>20.32237058624706</v>
+        <v>3.302385220265148</v>
       </c>
       <c r="F14" t="n">
-        <v>14.21747891189481</v>
+        <v>2.310340323182908</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
